--- a/wc-data.xlsx
+++ b/wc-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://croatiabankahr-my.sharepoint.com/personal/alberto_skendrovic_croatiabanka_hr1/Documents/Desktop/phc-stat/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="425" documentId="8_{31E65144-C7D6-482C-BFB9-14E83E95C2F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6CCC5297-1FA0-40D9-9A33-EF2D63F7DDCE}"/>
+  <xr:revisionPtr revIDLastSave="480" documentId="8_{31E65144-C7D6-482C-BFB9-14E83E95C2F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E042C87-7544-4D0C-97F4-FB9C95A12DFF}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{BABAC88A-431C-4718-AB57-202BD2B77C54}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="224">
   <si>
     <t>WCPQ</t>
   </si>
@@ -573,6 +573,144 @@
   </si>
   <si>
     <t>European Youth Olympic Festival</t>
+  </si>
+  <si>
+    <t>Datum</t>
+  </si>
+  <si>
+    <t>5.-13.5.2026.</t>
+  </si>
+  <si>
+    <t>20.-27.4.2024.</t>
+  </si>
+  <si>
+    <t>21.-28.4.2018.</t>
+  </si>
+  <si>
+    <t>19.-28.11.2015.</t>
+  </si>
+  <si>
+    <t>22.-29.11.2014.</t>
+  </si>
+  <si>
+    <t>22.-30.11.2013.</t>
+  </si>
+  <si>
+    <t>8.-15.12.2012.</t>
+  </si>
+  <si>
+    <t>3.-10.12.2011.</t>
+  </si>
+  <si>
+    <t>4.-11.12.2010.</t>
+  </si>
+  <si>
+    <t>5.-12.12.2009.</t>
+  </si>
+  <si>
+    <t>6.-13.12.2008.</t>
+  </si>
+  <si>
+    <t>1.-8.12.2007.</t>
+  </si>
+  <si>
+    <t>9.-16.12.2006.</t>
+  </si>
+  <si>
+    <t>9.-17.12.2005.</t>
+  </si>
+  <si>
+    <t>11.-18.12.2019.</t>
+  </si>
+  <si>
+    <t>8.-19.12.2024.</t>
+  </si>
+  <si>
+    <t>8.-19.12.2023.</t>
+  </si>
+  <si>
+    <t>26.4.-3.5.2025.</t>
+  </si>
+  <si>
+    <t>27.4.-4.5.2024.</t>
+  </si>
+  <si>
+    <t>29.4.-6.5.2023.</t>
+  </si>
+  <si>
+    <t>1.-6.5.2022.</t>
+  </si>
+  <si>
+    <t>12.-17.9.2021.</t>
+  </si>
+  <si>
+    <t>12.-17.4.2019.</t>
+  </si>
+  <si>
+    <t>11.-18.4.2018.</t>
+  </si>
+  <si>
+    <t>7.-13.5.2017.</t>
+  </si>
+  <si>
+    <t>25.4.-1.5.2016.</t>
+  </si>
+  <si>
+    <t>5.-10.10.2012.</t>
+  </si>
+  <si>
+    <t>12.-17.12.2015.</t>
+  </si>
+  <si>
+    <t>4.-11.10.2014.</t>
+  </si>
+  <si>
+    <t>7.-13.10.2013.</t>
+  </si>
+  <si>
+    <t>30.9.-8.10.2011.</t>
+  </si>
+  <si>
+    <t>24.-28.9.2010.</t>
+  </si>
+  <si>
+    <t>15.-22.10.2022.</t>
+  </si>
+  <si>
+    <t>12.-19.10.2019.</t>
+  </si>
+  <si>
+    <t>13.-20.10.2018.</t>
+  </si>
+  <si>
+    <t>6.-14.10.2017.</t>
+  </si>
+  <si>
+    <t>14.-22.10.2016.</t>
+  </si>
+  <si>
+    <t>30.9.-6.10.2012.</t>
+  </si>
+  <si>
+    <t>24.-29.9.2007.</t>
+  </si>
+  <si>
+    <t>18.-22.10.2005.</t>
+  </si>
+  <si>
+    <t>11.-15.2.2019.</t>
+  </si>
+  <si>
+    <t>20.-27.4.2019.</t>
+  </si>
+  <si>
+    <t>22.-29.4.2017.</t>
+  </si>
+  <si>
+    <t>4.-10.1.2026.</t>
+  </si>
+  <si>
+    <t>3.-7.12.2022.</t>
   </si>
 </sst>
 </file>
@@ -973,27 +1111,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{495383F2-5B11-4CBB-8C28-601B18F98C5F}">
-  <dimension ref="A1:O59"/>
+  <dimension ref="A1:P59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="3.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.77734375" style="1" customWidth="1"/>
     <col min="4" max="4" width="30.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="16.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.88671875" style="2"/>
+    <col min="5" max="5" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="16.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>153</v>
       </c>
@@ -1007,40 +1146,43 @@
         <v>167</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1053,41 +1195,44 @@
       <c r="D2" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F2" s="1">
         <v>2026</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="H2" s="1">
-        <v>11</v>
-      </c>
       <c r="I2" s="1">
+        <v>11</v>
+      </c>
+      <c r="J2" s="1">
         <v>17</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1100,41 +1245,44 @@
       <c r="D3" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F3" s="1">
         <v>2025</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
         <v>8</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>9</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1147,41 +1295,44 @@
       <c r="D4" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F4" s="1">
         <v>2024</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>5</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
         <v>8</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -1194,41 +1345,44 @@
       <c r="D5" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F5" s="1">
         <v>2023</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>6</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
         <v>8</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="N5" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="P5" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1241,41 +1395,44 @@
       <c r="D6" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F6" s="1">
         <v>2022</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>6</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>9</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="N6" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -1288,41 +1445,44 @@
       <c r="D7" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F7" s="1">
         <v>2021</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>7</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>10</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -1335,41 +1495,44 @@
       <c r="D8" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F8" s="1">
         <v>2019</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>8</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>10</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="O8" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="P8" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -1382,41 +1545,44 @@
       <c r="D9" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F9" s="1">
         <v>2018</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>7</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>8</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="N9" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="O9" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="P9" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -1429,41 +1595,44 @@
       <c r="D10" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F10" s="1">
         <v>2017</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <v>6</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>9</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="K10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="N10" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="O10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="P10" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -1476,41 +1645,44 @@
       <c r="D11" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F11" s="1">
         <v>2016</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <v>9</v>
       </c>
-      <c r="I11" s="1">
-        <v>11</v>
-      </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" s="1">
+        <v>11</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="N11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="O11" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="P11" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -1523,41 +1695,44 @@
       <c r="D12" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F12" s="1">
         <v>2015</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
         <v>25</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12" s="1">
         <v>26</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="K12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="L12" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="M12" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="N12" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="O12" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="O12" s="2" t="s">
+      <c r="P12" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
@@ -1570,41 +1745,44 @@
       <c r="D13" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F13" s="1">
         <v>2014</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
         <v>17</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13" s="1">
         <v>25</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="K13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="L13" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="M13" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="N13" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="O13" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="O13" s="2" t="s">
+      <c r="P13" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1617,41 +1795,44 @@
       <c r="D14" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F14" s="1">
         <v>2013</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="H14" s="1">
+      <c r="I14" s="1">
         <v>22</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14" s="1">
         <v>26</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="K14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="L14" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="M14" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="N14" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="O14" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="O14" s="2" t="s">
+      <c r="P14" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1664,41 +1845,44 @@
       <c r="D15" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F15" s="1">
         <v>2012</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H15" s="1">
+      <c r="I15" s="1">
         <v>16</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15" s="1">
         <v>26</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="L15" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="M15" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="N15" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="O15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="P15" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
@@ -1711,41 +1895,44 @@
       <c r="D16" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F16" s="1">
         <v>2012</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="H16" s="1">
+      <c r="I16" s="1">
         <v>2</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16" s="1">
         <v>7</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="K16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="L16" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L16" s="2" t="s">
+      <c r="M16" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="N16" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="O16" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="O16" s="2" t="s">
+      <c r="P16" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>10</v>
       </c>
@@ -1758,41 +1945,44 @@
       <c r="D17" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F17" s="1">
         <v>2011</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="H17" s="1">
-        <v>26</v>
       </c>
       <c r="I17" s="1">
         <v>26</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" s="1">
+        <v>26</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="L17" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L17" s="2" t="s">
+      <c r="M17" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="N17" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="O17" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="O17" s="2" t="s">
+      <c r="P17" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>10</v>
       </c>
@@ -1805,41 +1995,44 @@
       <c r="D18" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F18" s="1">
         <v>2010</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="H18" s="1">
+      <c r="I18" s="1">
         <v>24</v>
       </c>
-      <c r="I18" s="1">
+      <c r="J18" s="1">
         <v>25</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="K18" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="L18" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="M18" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="N18" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="O18" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O18" s="2" t="s">
+      <c r="P18" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>10</v>
       </c>
@@ -1852,41 +2045,44 @@
       <c r="D19" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F19" s="1">
         <v>2009</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H19" s="1">
+      <c r="I19" s="1">
         <v>23</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19" s="1">
         <v>30</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="K19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="L19" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="M19" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="N19" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="O19" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="O19" s="2" t="s">
+      <c r="P19" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
@@ -1899,41 +2095,44 @@
       <c r="D20" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F20" s="1">
         <v>2008</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="G20" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H20" s="1">
+      <c r="I20" s="1">
         <v>25</v>
       </c>
-      <c r="I20" s="1">
+      <c r="J20" s="1">
         <v>28</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="K20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="L20" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L20" s="2" t="s">
+      <c r="M20" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="N20" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="N20" s="2" t="s">
+      <c r="O20" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="O20" s="2" t="s">
+      <c r="P20" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -1946,41 +2145,44 @@
       <c r="D21" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F21" s="1">
         <v>2007</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="G21" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="H21" s="1">
+      <c r="I21" s="1">
         <v>20</v>
       </c>
-      <c r="I21" s="1">
+      <c r="J21" s="1">
         <v>31</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="K21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="L21" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L21" s="2" t="s">
+      <c r="M21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="N21" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="O21" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="O21" s="2" t="s">
+      <c r="P21" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>10</v>
       </c>
@@ -1993,41 +2195,44 @@
       <c r="D22" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F22" s="1">
         <v>2006</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="H22" s="1">
+      <c r="I22" s="1">
         <v>25</v>
       </c>
-      <c r="I22" s="1">
+      <c r="J22" s="1">
         <v>30</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="K22" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K22" s="2" t="s">
+      <c r="L22" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L22" s="2" t="s">
+      <c r="M22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="N22" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="N22" s="2" t="s">
+      <c r="O22" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="O22" s="2" t="s">
+      <c r="P22" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
@@ -2040,41 +2245,44 @@
       <c r="D23" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F23" s="1">
         <v>2005</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="G23" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="H23" s="1">
+      <c r="I23" s="1">
         <v>27</v>
       </c>
-      <c r="I23" s="1">
+      <c r="J23" s="1">
         <v>29</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="K23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K23" s="2" t="s">
+      <c r="L23" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L23" s="2" t="s">
+      <c r="M23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="N23" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="N23" s="2" t="s">
+      <c r="O23" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="O23" s="2" t="s">
+      <c r="P23" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
@@ -2087,41 +2295,44 @@
       <c r="D24" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F24" s="1">
         <v>2024</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="G24" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="H24" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="H24" s="1">
-        <v>10</v>
       </c>
       <c r="I24" s="1">
         <v>10</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="J24" s="1">
+        <v>10</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="L24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L24" s="2" t="s">
+      <c r="M24" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="N24" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="O24" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="O24" s="2" t="s">
+      <c r="P24" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>13</v>
       </c>
@@ -2134,41 +2345,44 @@
       <c r="D25" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F25" s="1">
         <v>2022</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="H25" s="1">
+      <c r="I25" s="1">
         <v>5</v>
       </c>
-      <c r="I25" s="1">
+      <c r="J25" s="1">
         <v>8</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="K25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K25" s="2" t="s">
+      <c r="L25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L25" s="2" t="s">
+      <c r="M25" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M25" s="2" t="s">
+      <c r="N25" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="N25" s="2" t="s">
+      <c r="O25" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="O25" s="2" t="s">
+      <c r="P25" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>13</v>
       </c>
@@ -2181,41 +2395,44 @@
       <c r="D26" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F26" s="1">
         <v>2019</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="G26" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="H26" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="H26" s="1">
+      <c r="I26" s="1">
         <v>7</v>
       </c>
-      <c r="I26" s="1">
+      <c r="J26" s="1">
         <v>8</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="K26" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="L26" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L26" s="2" t="s">
+      <c r="M26" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M26" s="2" t="s">
+      <c r="N26" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="N26" s="2" t="s">
+      <c r="O26" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="O26" s="2" t="s">
+      <c r="P26" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>13</v>
       </c>
@@ -2228,41 +2445,44 @@
       <c r="D27" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F27" s="1">
         <v>2018</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="G27" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="H27" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="H27" s="1">
+      <c r="I27" s="1">
         <v>6</v>
       </c>
-      <c r="I27" s="1">
+      <c r="J27" s="1">
         <v>7</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="K27" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="K27" s="2" t="s">
+      <c r="L27" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L27" s="2" t="s">
+      <c r="M27" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M27" s="2" t="s">
+      <c r="N27" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="N27" s="2" t="s">
+      <c r="O27" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="O27" s="2" t="s">
+      <c r="P27" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>13</v>
       </c>
@@ -2275,41 +2495,44 @@
       <c r="D28" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E28" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F28" s="1">
         <v>2017</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="G28" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="H28" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H28" s="1">
+      <c r="I28" s="1">
         <v>6</v>
       </c>
-      <c r="I28" s="1">
+      <c r="J28" s="1">
         <v>8</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="K28" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K28" s="2" t="s">
+      <c r="L28" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L28" s="2" t="s">
+      <c r="M28" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M28" s="2" t="s">
+      <c r="N28" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="N28" s="2" t="s">
+      <c r="O28" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="O28" s="2" t="s">
+      <c r="P28" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>13</v>
       </c>
@@ -2322,41 +2545,44 @@
       <c r="D29" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F29" s="1">
         <v>2016</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="G29" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="H29" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="H29" s="1">
+      <c r="I29" s="1">
         <v>5</v>
       </c>
-      <c r="I29" s="1">
+      <c r="J29" s="1">
         <v>8</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="K29" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K29" s="2" t="s">
+      <c r="L29" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="L29" s="2" t="s">
+      <c r="M29" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="M29" s="2" t="s">
+      <c r="N29" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="N29" s="2" t="s">
+      <c r="O29" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="O29" s="2" t="s">
+      <c r="P29" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>13</v>
       </c>
@@ -2369,41 +2595,44 @@
       <c r="D30" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F30" s="1">
         <v>2015</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="G30" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="H30" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="H30" s="1">
+      <c r="I30" s="1">
         <v>7</v>
       </c>
-      <c r="I30" s="1">
+      <c r="J30" s="1">
         <v>8</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="K30" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="K30" s="2" t="s">
+      <c r="L30" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L30" s="2" t="s">
+      <c r="M30" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M30" s="2" t="s">
+      <c r="N30" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="N30" s="2" t="s">
+      <c r="O30" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="O30" s="2" t="s">
+      <c r="P30" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>13</v>
       </c>
@@ -2416,41 +2645,44 @@
       <c r="D31" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E31" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F31" s="1">
         <v>2014</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="G31" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="H31" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="H31" s="1">
+      <c r="I31" s="1">
         <v>5</v>
       </c>
-      <c r="I31" s="1">
+      <c r="J31" s="1">
         <v>7</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="K31" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="K31" s="2" t="s">
+      <c r="L31" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="L31" s="2" t="s">
+      <c r="M31" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="N31" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="N31" s="2" t="s">
+      <c r="O31" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="O31" s="2" t="s">
+      <c r="P31" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>13</v>
       </c>
@@ -2463,41 +2695,44 @@
       <c r="D32" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F32" s="1">
         <v>2013</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="G32" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="H32" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="H32" s="1">
-        <v>4</v>
       </c>
       <c r="I32" s="1">
         <v>4</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="J32" s="1">
+        <v>4</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="K32" s="2" t="s">
+      <c r="L32" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L32" s="2" t="s">
+      <c r="M32" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M32" s="2" t="s">
+      <c r="N32" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="N32" s="2" t="s">
+      <c r="O32" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="O32" s="2" t="s">
+      <c r="P32" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>13</v>
       </c>
@@ -2510,41 +2745,44 @@
       <c r="D33" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F33" s="1">
         <v>2012</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="G33" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="H33" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="H33" s="1">
+      <c r="I33" s="1">
         <v>4</v>
       </c>
-      <c r="I33" s="1">
+      <c r="J33" s="1">
         <v>6</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="K33" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="K33" s="2" t="s">
+      <c r="L33" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="L33" s="2" t="s">
+      <c r="M33" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="M33" s="2" t="s">
+      <c r="N33" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="N33" s="2" t="s">
+      <c r="O33" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="O33" s="2" t="s">
+      <c r="P33" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>13</v>
       </c>
@@ -2557,41 +2795,44 @@
       <c r="D34" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F34" s="1">
         <v>2011</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="G34" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="H34" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="H34" s="1">
-        <v>10</v>
       </c>
       <c r="I34" s="1">
         <v>10</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="J34" s="1">
+        <v>10</v>
+      </c>
+      <c r="K34" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="L34" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L34" s="2" t="s">
+      <c r="M34" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M34" s="2" t="s">
+      <c r="N34" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="N34" s="2" t="s">
+      <c r="O34" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="O34" s="2" t="s">
+      <c r="P34" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>13</v>
       </c>
@@ -2604,38 +2845,41 @@
       <c r="D35" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F35" s="1">
         <v>2010</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="G35" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="H35" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H35" s="1">
+      <c r="I35" s="1">
         <v>4</v>
       </c>
-      <c r="J35" s="1" t="s">
+      <c r="K35" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="K35" s="2" t="s">
+      <c r="L35" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="L35" s="2" t="s">
+      <c r="M35" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="M35" s="2" t="s">
+      <c r="N35" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="N35" s="2" t="s">
+      <c r="O35" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="O35" s="2" t="s">
+      <c r="P35" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>13</v>
       </c>
@@ -2648,41 +2892,44 @@
       <c r="D36" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F36" s="1">
         <v>2009</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="G36" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="H36" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="H36" s="1">
-        <v>21</v>
       </c>
       <c r="I36" s="1">
         <v>21</v>
       </c>
-      <c r="J36" s="1" t="s">
+      <c r="J36" s="1">
+        <v>21</v>
+      </c>
+      <c r="K36" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K36" s="2" t="s">
+      <c r="L36" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="L36" s="2" t="s">
+      <c r="M36" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="M36" s="2" t="s">
+      <c r="N36" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="N36" s="2" t="s">
+      <c r="O36" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="O36" s="2" t="s">
+      <c r="P36" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>13</v>
       </c>
@@ -2695,41 +2942,44 @@
       <c r="D37" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E37" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F37" s="1">
         <v>2008</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="G37" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="H37" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H37" s="1">
+      <c r="I37" s="1">
         <v>19</v>
       </c>
-      <c r="I37" s="1">
+      <c r="J37" s="1">
         <v>21</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="K37" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K37" s="2" t="s">
+      <c r="L37" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="L37" s="2" t="s">
+      <c r="M37" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="M37" s="2" t="s">
+      <c r="N37" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="N37" s="2" t="s">
+      <c r="O37" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="O37" s="2" t="s">
+      <c r="P37" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>13</v>
       </c>
@@ -2742,41 +2992,44 @@
       <c r="D38" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E38" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F38" s="1">
         <v>2007</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="G38" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="H38" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="H38" s="1">
+      <c r="I38" s="1">
         <v>17</v>
       </c>
-      <c r="I38" s="1">
+      <c r="J38" s="1">
         <v>23</v>
       </c>
-      <c r="J38" s="1" t="s">
+      <c r="K38" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K38" s="2" t="s">
+      <c r="L38" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="L38" s="2" t="s">
+      <c r="M38" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="M38" s="2" t="s">
+      <c r="N38" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="N38" s="2" t="s">
+      <c r="O38" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="O38" s="2" t="s">
+      <c r="P38" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>13</v>
       </c>
@@ -2789,41 +3042,44 @@
       <c r="D39" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E39" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F39" s="1">
         <v>2006</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="G39" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="H39" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="H39" s="1">
+      <c r="I39" s="1">
         <v>21</v>
       </c>
-      <c r="I39" s="1">
+      <c r="J39" s="1">
         <v>22</v>
       </c>
-      <c r="J39" s="1" t="s">
+      <c r="K39" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K39" s="2" t="s">
+      <c r="L39" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="L39" s="2" t="s">
+      <c r="M39" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="M39" s="2" t="s">
+      <c r="N39" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="N39" s="2" t="s">
+      <c r="O39" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="O39" s="2" t="s">
+      <c r="P39" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>13</v>
       </c>
@@ -2836,38 +3092,41 @@
       <c r="D40" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E40" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F40" s="1">
         <v>2005</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="G40" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="H40" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="H40" s="1">
+      <c r="I40" s="1">
         <v>19</v>
       </c>
-      <c r="I40" s="1">
+      <c r="J40" s="1">
         <v>24</v>
       </c>
-      <c r="J40" s="1" t="s">
+      <c r="K40" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="K40" s="2" t="s">
+      <c r="L40" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="L40" s="2" t="s">
+      <c r="M40" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="M40" s="2" t="s">
+      <c r="N40" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="N40" s="2" t="s">
+      <c r="O40" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>14</v>
       </c>
@@ -2880,38 +3139,41 @@
       <c r="D41" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E41" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F41" s="1">
         <v>2022</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="G41" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="H41" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H41" s="1">
+      <c r="I41" s="1">
         <v>32</v>
       </c>
-      <c r="I41" s="1">
+      <c r="J41" s="1">
         <v>35</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="K41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K41" s="2" t="s">
+      <c r="L41" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="L41" s="2" t="s">
+      <c r="M41" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="M41" s="2" t="s">
+      <c r="N41" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="N41" s="2" t="s">
+      <c r="O41" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>14</v>
       </c>
@@ -2924,38 +3186,41 @@
       <c r="D42" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E42" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F42" s="1">
         <v>2019</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="G42" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="H42" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H42" s="1">
+      <c r="I42" s="1">
         <v>35</v>
       </c>
-      <c r="I42" s="1">
+      <c r="J42" s="1">
         <v>40</v>
       </c>
-      <c r="J42" s="1" t="s">
+      <c r="K42" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K42" s="2" t="s">
+      <c r="L42" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="L42" s="2" t="s">
+      <c r="M42" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="M42" s="2" t="s">
+      <c r="N42" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="N42" s="2" t="s">
+      <c r="O42" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>14</v>
       </c>
@@ -2968,38 +3233,41 @@
       <c r="D43" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E43" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F43" s="1">
         <v>2018</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="G43" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="H43" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="H43" s="1">
-        <v>35</v>
       </c>
       <c r="I43" s="1">
         <v>35</v>
       </c>
-      <c r="J43" s="1" t="s">
+      <c r="J43" s="1">
+        <v>35</v>
+      </c>
+      <c r="K43" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K43" s="2" t="s">
+      <c r="L43" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L43" s="2" t="s">
+      <c r="M43" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="M43" s="2" t="s">
+      <c r="N43" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="N43" s="2" t="s">
+      <c r="O43" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>14</v>
       </c>
@@ -3012,38 +3280,41 @@
       <c r="D44" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F44" s="1">
         <v>2017</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="G44" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="H44" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="H44" s="1">
+      <c r="I44" s="1">
         <v>29</v>
       </c>
-      <c r="I44" s="1">
+      <c r="J44" s="1">
         <v>37</v>
       </c>
-      <c r="J44" s="1" t="s">
+      <c r="K44" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K44" s="2" t="s">
+      <c r="L44" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L44" s="2" t="s">
+      <c r="M44" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="M44" s="2" t="s">
+      <c r="N44" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="N44" s="2" t="s">
+      <c r="O44" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>14</v>
       </c>
@@ -3056,38 +3327,41 @@
       <c r="D45" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E45" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F45" s="1">
         <v>2016</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="G45" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="H45" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="H45" s="1">
+      <c r="I45" s="1">
         <v>30</v>
       </c>
-      <c r="I45" s="1">
+      <c r="J45" s="1">
         <v>37</v>
       </c>
-      <c r="J45" s="1" t="s">
+      <c r="K45" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="K45" s="2" t="s">
+      <c r="L45" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L45" s="2" t="s">
+      <c r="M45" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M45" s="2" t="s">
+      <c r="N45" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="N45" s="2" t="s">
+      <c r="O45" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>14</v>
       </c>
@@ -3100,41 +3374,44 @@
       <c r="D46" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E46" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F46" s="1">
         <v>2012</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="G46" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="H46" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="H46" s="1">
-        <v>24</v>
       </c>
       <c r="I46" s="1">
         <v>24</v>
       </c>
-      <c r="J46" s="1" t="s">
+      <c r="J46" s="1">
+        <v>24</v>
+      </c>
+      <c r="K46" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K46" s="2" t="s">
+      <c r="L46" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="L46" s="2" t="s">
+      <c r="M46" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M46" s="2" t="s">
+      <c r="N46" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="N46" s="2" t="s">
+      <c r="O46" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="O46" s="2" t="s">
+      <c r="P46" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>14</v>
       </c>
@@ -3147,38 +3424,41 @@
       <c r="D47" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F47" s="1">
         <v>2007</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="G47" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="H47" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="H47" s="1">
-        <v>24</v>
       </c>
       <c r="I47" s="1">
         <v>24</v>
       </c>
-      <c r="J47" s="1" t="s">
+      <c r="J47" s="1">
+        <v>24</v>
+      </c>
+      <c r="K47" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K47" s="2" t="s">
+      <c r="L47" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L47" s="2" t="s">
+      <c r="M47" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="M47" s="2" t="s">
+      <c r="N47" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="N47" s="2" t="s">
+      <c r="O47" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>14</v>
       </c>
@@ -3191,38 +3471,41 @@
       <c r="D48" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E48" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F48" s="1">
         <v>2005</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="G48" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="H48" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H48" s="1">
+      <c r="I48" s="1">
         <v>22</v>
       </c>
-      <c r="I48" s="1">
+      <c r="J48" s="1">
         <v>23</v>
       </c>
-      <c r="J48" s="1" t="s">
+      <c r="K48" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K48" s="2" t="s">
+      <c r="L48" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L48" s="2" t="s">
+      <c r="M48" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="M48" s="2" t="s">
+      <c r="N48" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="N48" s="2" t="s">
+      <c r="O48" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>15</v>
       </c>
@@ -3235,32 +3518,35 @@
       <c r="D49" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E49" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F49" s="1">
         <v>2026</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="G49" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="H49" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H49" s="1">
+      <c r="I49" s="1">
         <v>27</v>
       </c>
-      <c r="I49" s="1">
+      <c r="J49" s="1">
         <v>33</v>
       </c>
-      <c r="J49" s="1" t="s">
+      <c r="K49" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K49" s="2" t="s">
+      <c r="L49" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L49" s="2" t="s">
+      <c r="M49" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>15</v>
       </c>
@@ -3273,32 +3559,35 @@
       <c r="D50" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E50" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F50" s="1">
         <v>2022</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="G50" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="H50" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H50" s="1">
+      <c r="I50" s="1">
         <v>24</v>
       </c>
-      <c r="I50" s="1">
+      <c r="J50" s="1">
         <v>26</v>
       </c>
-      <c r="J50" s="1" t="s">
+      <c r="K50" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K50" s="2" t="s">
+      <c r="L50" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="L50" s="2" t="s">
+      <c r="M50" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>15</v>
       </c>
@@ -3311,32 +3600,35 @@
       <c r="D51" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E51" s="1">
+      <c r="E51" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F51" s="1">
         <v>2019</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="G51" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="H51" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="H51" s="1">
+      <c r="I51" s="1">
         <v>41</v>
       </c>
-      <c r="I51" s="1">
+      <c r="J51" s="1">
         <v>48</v>
       </c>
-      <c r="J51" s="1" t="s">
+      <c r="K51" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K51" s="2" t="s">
+      <c r="L51" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="L51" s="2" t="s">
+      <c r="M51" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>15</v>
       </c>
@@ -3349,32 +3641,35 @@
       <c r="D52" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E52" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F52" s="1">
         <v>2018</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="G52" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="H52" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="H52" s="1">
-        <v>40</v>
       </c>
       <c r="I52" s="1">
         <v>40</v>
       </c>
-      <c r="J52" s="1" t="s">
+      <c r="J52" s="1">
+        <v>40</v>
+      </c>
+      <c r="K52" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K52" s="2" t="s">
+      <c r="L52" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="L52" s="2" t="s">
+      <c r="M52" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>15</v>
       </c>
@@ -3387,32 +3682,35 @@
       <c r="D53" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E53" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F53" s="1">
         <v>2017</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="G53" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="H53" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H53" s="1">
+      <c r="I53" s="1">
         <v>37</v>
       </c>
-      <c r="I53" s="1">
+      <c r="J53" s="1">
         <v>39</v>
       </c>
-      <c r="J53" s="1" t="s">
+      <c r="K53" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K53" s="2" t="s">
+      <c r="L53" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L53" s="2" t="s">
+      <c r="M53" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>10</v>
       </c>
@@ -3425,41 +3723,44 @@
       <c r="D54" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E54" s="1">
+      <c r="E54" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F54" s="1">
         <v>2019</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="G54" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="H54" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="H54" s="1">
-        <v>24</v>
       </c>
       <c r="I54" s="1">
         <v>24</v>
       </c>
-      <c r="J54" s="1" t="s">
+      <c r="J54" s="1">
+        <v>24</v>
+      </c>
+      <c r="K54" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K54" s="2" t="s">
+      <c r="L54" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="L54" s="2" t="s">
+      <c r="M54" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="M54" s="2" t="s">
+      <c r="N54" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="N54" s="2" t="s">
+      <c r="O54" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="O54" s="2" t="s">
+      <c r="P54" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>13</v>
       </c>
@@ -3472,41 +3773,44 @@
       <c r="D55" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E55" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F55" s="1">
         <v>2024</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="G55" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="H55" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="H55" s="1">
-        <v>21</v>
       </c>
       <c r="I55" s="1">
         <v>21</v>
       </c>
-      <c r="J55" s="1" t="s">
+      <c r="J55" s="1">
+        <v>21</v>
+      </c>
+      <c r="K55" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K55" s="2" t="s">
+      <c r="L55" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="L55" s="2" t="s">
+      <c r="M55" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="M55" s="2" t="s">
+      <c r="N55" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="N55" s="2" t="s">
+      <c r="O55" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="O55" s="2" t="s">
+      <c r="P55" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>13</v>
       </c>
@@ -3519,41 +3823,44 @@
       <c r="D56" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E56" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F56" s="1">
         <v>2023</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="G56" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="H56" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="H56" s="1">
+      <c r="I56" s="1">
         <v>24</v>
       </c>
-      <c r="I56" s="1">
+      <c r="J56" s="1">
         <v>25</v>
       </c>
-      <c r="J56" s="1" t="s">
+      <c r="K56" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K56" s="2" t="s">
+      <c r="L56" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="L56" s="2" t="s">
+      <c r="M56" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="M56" s="2" t="s">
+      <c r="N56" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="N56" s="2" t="s">
+      <c r="O56" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="O56" s="2" t="s">
+      <c r="P56" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>14</v>
       </c>
@@ -3566,38 +3873,41 @@
       <c r="D57" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E57" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F57" s="1">
         <v>2019</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="G57" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="G57" s="1" t="s">
+      <c r="H57" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="H57" s="1">
-        <v>14</v>
       </c>
       <c r="I57" s="1">
         <v>14</v>
       </c>
-      <c r="J57" s="1" t="s">
+      <c r="J57" s="1">
+        <v>14</v>
+      </c>
+      <c r="K57" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K57" s="2" t="s">
+      <c r="L57" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="L57" s="2" t="s">
+      <c r="M57" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="M57" s="2" t="s">
+      <c r="N57" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="N57" s="2" t="s">
+      <c r="O57" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>10</v>
       </c>
@@ -3610,41 +3920,44 @@
       <c r="D58" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E58" s="1">
+      <c r="E58" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F58" s="1">
         <v>2024</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="G58" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G58" s="1" t="s">
+      <c r="H58" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H58" s="1">
+      <c r="I58" s="1">
         <v>22</v>
       </c>
-      <c r="I58" s="1">
+      <c r="J58" s="1">
         <v>25</v>
       </c>
-      <c r="J58" s="1" t="s">
+      <c r="K58" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="K58" s="2" t="s">
+      <c r="L58" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="L58" s="2" t="s">
+      <c r="M58" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="M58" s="2" t="s">
+      <c r="N58" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="N58" s="2" t="s">
+      <c r="O58" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="O58" s="2" t="s">
+      <c r="P58" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>10</v>
       </c>
@@ -3657,40 +3970,43 @@
       <c r="D59" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E59" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F59" s="1">
         <v>2018</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="G59" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G59" s="1" t="s">
+      <c r="H59" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="H59" s="1">
-        <v>28</v>
       </c>
       <c r="I59" s="1">
         <v>28</v>
       </c>
-      <c r="J59" s="1" t="s">
+      <c r="J59" s="1">
+        <v>28</v>
+      </c>
+      <c r="K59" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K59" s="2" t="s">
+      <c r="L59" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="L59" s="2" t="s">
+      <c r="M59" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="M59" s="2" t="s">
+      <c r="N59" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="N59" s="2" t="s">
+      <c r="O59" s="2" t="s">
         <v>70</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A41:J48">
-    <sortCondition descending="1" ref="E41:E48"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A41:K48">
+    <sortCondition descending="1" ref="F41:F48"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/wc-data.xlsx
+++ b/wc-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://croatiabankahr-my.sharepoint.com/personal/alberto_skendrovic_croatiabanka_hr1/Documents/Desktop/phc-stat/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c9d1b39c11dd659/Dokumenti/Apps/phc-stat/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="480" documentId="8_{31E65144-C7D6-482C-BFB9-14E83E95C2F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E042C87-7544-4D0C-97F4-FB9C95A12DFF}"/>
+  <xr:revisionPtr revIDLastSave="652" documentId="8_{31E65144-C7D6-482C-BFB9-14E83E95C2F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{304FED25-3186-4C9F-95F9-AA938F387331}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{BABAC88A-431C-4718-AB57-202BD2B77C54}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{BABAC88A-431C-4718-AB57-202BD2B77C54}"/>
   </bookViews>
   <sheets>
     <sheet name="Curling" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="245">
   <si>
     <t>WCPQ</t>
   </si>
@@ -659,9 +659,6 @@
     <t>5.-10.10.2012.</t>
   </si>
   <si>
-    <t>12.-17.12.2015.</t>
-  </si>
-  <si>
     <t>4.-11.10.2014.</t>
   </si>
   <si>
@@ -711,6 +708,72 @@
   </si>
   <si>
     <t>3.-7.12.2022.</t>
+  </si>
+  <si>
+    <t>WCDB</t>
+  </si>
+  <si>
+    <t>2025-2026</t>
+  </si>
+  <si>
+    <t>12.-17.10.2015.</t>
+  </si>
+  <si>
+    <t>2024-2025</t>
+  </si>
+  <si>
+    <t>2023-2024</t>
+  </si>
+  <si>
+    <t>2022-2023</t>
+  </si>
+  <si>
+    <t>2021-2022</t>
+  </si>
+  <si>
+    <t>2018-2019</t>
+  </si>
+  <si>
+    <t>2017-2018</t>
+  </si>
+  <si>
+    <t>2016-2017</t>
+  </si>
+  <si>
+    <t>2015-2016</t>
+  </si>
+  <si>
+    <t>2014-2015</t>
+  </si>
+  <si>
+    <t>2013-2014</t>
+  </si>
+  <si>
+    <t>2012-2013</t>
+  </si>
+  <si>
+    <t>2011-2012</t>
+  </si>
+  <si>
+    <t>2010-2011</t>
+  </si>
+  <si>
+    <t>2009-2010</t>
+  </si>
+  <si>
+    <t>2008-2009</t>
+  </si>
+  <si>
+    <t>2007-2008</t>
+  </si>
+  <si>
+    <t>2006-2007</t>
+  </si>
+  <si>
+    <t>2005-2006</t>
+  </si>
+  <si>
+    <t>2019-2020</t>
   </si>
 </sst>
 </file>
@@ -792,6 +855,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1111,28 +1178,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{495383F2-5B11-4CBB-8C28-601B18F98C5F}">
-  <dimension ref="A1:P59"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q59"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.77734375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="21.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="16.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="34.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="18" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>153</v>
       </c>
@@ -1152,37 +1220,40 @@
         <v>156</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1198,41 +1269,44 @@
       <c r="E2" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="F2" s="1">
-        <v>2026</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G2" s="1">
+        <v>839</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="I2" s="1">
-        <v>11</v>
-      </c>
       <c r="J2" s="1">
+        <v>11</v>
+      </c>
+      <c r="K2" s="1">
         <v>17</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1248,41 +1322,44 @@
       <c r="E3" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F3" s="1">
-        <v>2025</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="F3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G3" s="1">
+        <v>795</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>8</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K3" s="1">
         <v>9</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1298,41 +1375,44 @@
       <c r="E4" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="F4" s="1">
-        <v>2024</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G4" s="1">
+        <v>768</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
         <v>5</v>
       </c>
-      <c r="J4" s="1">
+      <c r="K4" s="1">
         <v>8</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -1348,41 +1428,44 @@
       <c r="E5" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="F5" s="1">
-        <v>2023</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="F5" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G5" s="1">
+        <v>742</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
         <v>6</v>
       </c>
-      <c r="J5" s="1">
+      <c r="K5" s="1">
         <v>8</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="N5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="P5" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="Q5" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1398,41 +1481,44 @@
       <c r="E6" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="F6" s="1">
-        <v>2022</v>
-      </c>
-      <c r="G6" s="1" t="s">
+      <c r="F6" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G6" s="1">
+        <v>715</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>6</v>
       </c>
-      <c r="J6" s="1">
+      <c r="K6" s="1">
         <v>9</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="N6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -1448,41 +1534,44 @@
       <c r="E7" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F7" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G7" s="1" t="s">
+      <c r="F7" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G7" s="1">
+        <v>680</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>7</v>
       </c>
-      <c r="J7" s="1">
+      <c r="K7" s="1">
         <v>10</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -1498,41 +1587,44 @@
       <c r="E8" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F8" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G8" s="1" t="s">
+      <c r="F8" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G8" s="1">
+        <v>645</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>8</v>
       </c>
-      <c r="J8" s="1">
+      <c r="K8" s="1">
         <v>10</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="L8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="O8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="P8" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="P8" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -1548,41 +1640,44 @@
       <c r="E9" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="F9" s="1">
-        <v>2018</v>
-      </c>
-      <c r="G9" s="1" t="s">
+      <c r="F9" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G9" s="1">
+        <v>609</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>7</v>
       </c>
-      <c r="J9" s="1">
+      <c r="K9" s="1">
         <v>8</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="N9" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="O9" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="P9" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="Q9" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -1598,41 +1693,44 @@
       <c r="E10" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="F10" s="1">
-        <v>2017</v>
-      </c>
-      <c r="G10" s="1" t="s">
+      <c r="F10" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G10" s="1">
+        <v>591</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>6</v>
       </c>
-      <c r="J10" s="1">
+      <c r="K10" s="1">
         <v>9</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="N10" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="O10" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="P10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="P10" s="2" t="s">
+      <c r="Q10" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -1648,41 +1746,44 @@
       <c r="E11" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F11" s="1">
-        <v>2016</v>
-      </c>
-      <c r="G11" s="1" t="s">
+      <c r="F11" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="G11" s="1">
+        <v>563</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11" s="1">
         <v>9</v>
       </c>
-      <c r="J11" s="1">
-        <v>11</v>
-      </c>
-      <c r="K11" s="1" t="s">
+      <c r="K11" s="1">
+        <v>11</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="N11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="O11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="P11" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="P11" s="2" t="s">
+      <c r="Q11" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -1698,41 +1799,44 @@
       <c r="E12" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F12" s="1">
-        <v>2015</v>
-      </c>
-      <c r="G12" s="1" t="s">
+      <c r="F12" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="G12" s="1">
+        <v>547</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12" s="1">
         <v>25</v>
       </c>
-      <c r="J12" s="1">
+      <c r="K12" s="1">
         <v>26</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="M12" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="N12" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="O12" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="O12" s="2" t="s">
+      <c r="P12" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="P12" s="2" t="s">
+      <c r="Q12" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
@@ -1748,41 +1852,44 @@
       <c r="E13" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="F13" s="1">
-        <v>2014</v>
-      </c>
-      <c r="G13" s="1" t="s">
+      <c r="F13" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G13" s="1">
+        <v>522</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13" s="1">
         <v>17</v>
       </c>
-      <c r="J13" s="1">
+      <c r="K13" s="1">
         <v>25</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="M13" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="N13" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="O13" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="O13" s="2" t="s">
+      <c r="P13" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="P13" s="2" t="s">
+      <c r="Q13" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1798,41 +1905,44 @@
       <c r="E14" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F14" s="1">
-        <v>2013</v>
-      </c>
-      <c r="G14" s="1" t="s">
+      <c r="F14" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="G14" s="1">
+        <v>491</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14" s="1">
         <v>22</v>
       </c>
-      <c r="J14" s="1">
+      <c r="K14" s="1">
         <v>26</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="M14" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="N14" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="O14" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="O14" s="2" t="s">
+      <c r="P14" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="P14" s="2" t="s">
+      <c r="Q14" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1848,41 +1958,44 @@
       <c r="E15" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F15" s="1">
-        <v>2012</v>
-      </c>
-      <c r="G15" s="1" t="s">
+      <c r="F15" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G15" s="1">
+        <v>451</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15" s="1">
         <v>16</v>
       </c>
-      <c r="J15" s="1">
+      <c r="K15" s="1">
         <v>26</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="M15" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="N15" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="O15" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="P15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P15" s="2" t="s">
+      <c r="Q15" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
@@ -1898,41 +2011,44 @@
       <c r="E16" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F16" s="1">
-        <v>2012</v>
-      </c>
-      <c r="G16" s="1" t="s">
+      <c r="F16" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G16" s="1">
+        <v>467</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16" s="1">
         <v>2</v>
       </c>
-      <c r="J16" s="1">
+      <c r="K16" s="1">
         <v>7</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L16" s="2" t="s">
+      <c r="M16" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="N16" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="O16" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="O16" s="2" t="s">
+      <c r="P16" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="P16" s="2" t="s">
+      <c r="Q16" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>10</v>
       </c>
@@ -1948,41 +2064,44 @@
       <c r="E17" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="F17" s="1">
-        <v>2011</v>
-      </c>
-      <c r="G17" s="1" t="s">
+      <c r="F17" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G17" s="1">
+        <v>435</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="I17" s="1">
-        <v>26</v>
       </c>
       <c r="J17" s="1">
         <v>26</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="K17" s="1">
+        <v>26</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L17" s="2" t="s">
+      <c r="M17" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="N17" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="O17" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="O17" s="2" t="s">
+      <c r="P17" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="P17" s="2" t="s">
+      <c r="Q17" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>10</v>
       </c>
@@ -1998,41 +2117,44 @@
       <c r="E18" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="F18" s="1">
-        <v>2010</v>
-      </c>
-      <c r="G18" s="1" t="s">
+      <c r="F18" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="G18" s="1">
+        <v>359</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="I18" s="1">
+      <c r="J18" s="1">
         <v>24</v>
       </c>
-      <c r="J18" s="1">
+      <c r="K18" s="1">
         <v>25</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="L18" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="M18" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="N18" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="O18" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="O18" s="2" t="s">
+      <c r="P18" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="P18" s="2" t="s">
+      <c r="Q18" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>10</v>
       </c>
@@ -2048,41 +2170,44 @@
       <c r="E19" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F19" s="1">
-        <v>2009</v>
-      </c>
-      <c r="G19" s="1" t="s">
+      <c r="F19" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="G19" s="1">
+        <v>318</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19" s="1">
         <v>23</v>
       </c>
-      <c r="J19" s="1">
+      <c r="K19" s="1">
         <v>30</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="M19" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="N19" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="O19" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="O19" s="2" t="s">
+      <c r="P19" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="P19" s="2" t="s">
+      <c r="Q19" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
@@ -2098,41 +2223,44 @@
       <c r="E20" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F20" s="1">
-        <v>2008</v>
-      </c>
-      <c r="G20" s="1" t="s">
+      <c r="F20" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="G20" s="1">
+        <v>253</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="I20" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I20" s="1">
+      <c r="J20" s="1">
         <v>25</v>
       </c>
-      <c r="J20" s="1">
+      <c r="K20" s="1">
         <v>28</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="L20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="L20" s="2" t="s">
+      <c r="M20" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="N20" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="N20" s="2" t="s">
+      <c r="O20" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="O20" s="2" t="s">
+      <c r="P20" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="P20" s="2" t="s">
+      <c r="Q20" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -2148,41 +2276,44 @@
       <c r="E21" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F21" s="1">
-        <v>2007</v>
-      </c>
-      <c r="G21" s="1" t="s">
+      <c r="F21" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G21" s="1">
+        <v>320</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I21" s="1">
+      <c r="J21" s="1">
         <v>20</v>
       </c>
-      <c r="J21" s="1">
+      <c r="K21" s="1">
         <v>31</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L21" s="2" t="s">
+      <c r="M21" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="N21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="O21" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="O21" s="2" t="s">
+      <c r="P21" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="P21" s="2" t="s">
+      <c r="Q21" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>10</v>
       </c>
@@ -2198,41 +2329,44 @@
       <c r="E22" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="F22" s="1">
-        <v>2006</v>
-      </c>
-      <c r="G22" s="1" t="s">
+      <c r="F22" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G22" s="1">
+        <v>231</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="I22" s="1">
+      <c r="J22" s="1">
         <v>25</v>
       </c>
-      <c r="J22" s="1">
+      <c r="K22" s="1">
         <v>30</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="L22" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L22" s="2" t="s">
+      <c r="M22" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="N22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="N22" s="2" t="s">
+      <c r="O22" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="O22" s="2" t="s">
+      <c r="P22" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="P22" s="2" t="s">
+      <c r="Q22" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
@@ -2248,41 +2382,44 @@
       <c r="E23" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F23" s="1">
-        <v>2005</v>
-      </c>
-      <c r="G23" s="1" t="s">
+      <c r="F23" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G23" s="1">
+        <v>229</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I23" s="1">
+      <c r="J23" s="1">
         <v>27</v>
       </c>
-      <c r="J23" s="1">
+      <c r="K23" s="1">
         <v>29</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="L23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L23" s="2" t="s">
+      <c r="M23" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="N23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="N23" s="2" t="s">
+      <c r="O23" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="O23" s="2" t="s">
+      <c r="P23" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="P23" s="2" t="s">
+      <c r="Q23" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
@@ -2298,41 +2435,44 @@
       <c r="E24" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="F24" s="1">
-        <v>2024</v>
-      </c>
-      <c r="G24" s="1" t="s">
+      <c r="F24" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G24" s="1">
+        <v>769</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="I24" s="1">
-        <v>10</v>
       </c>
       <c r="J24" s="1">
         <v>10</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="K24" s="1">
+        <v>10</v>
+      </c>
+      <c r="L24" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L24" s="2" t="s">
+      <c r="M24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="N24" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="O24" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="O24" s="2" t="s">
+      <c r="P24" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="P24" s="2" t="s">
+      <c r="Q24" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>13</v>
       </c>
@@ -2348,41 +2488,44 @@
       <c r="E25" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="F25" s="1">
-        <v>2022</v>
-      </c>
-      <c r="G25" s="1" t="s">
+      <c r="F25" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G25" s="1">
+        <v>716</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="I25" s="1">
+      <c r="J25" s="1">
         <v>5</v>
       </c>
-      <c r="J25" s="1">
+      <c r="K25" s="1">
         <v>8</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="L25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L25" s="2" t="s">
+      <c r="M25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="M25" s="2" t="s">
+      <c r="N25" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N25" s="2" t="s">
+      <c r="O25" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="O25" s="2" t="s">
+      <c r="P25" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="P25" s="2" t="s">
+      <c r="Q25" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>13</v>
       </c>
@@ -2398,41 +2541,44 @@
       <c r="E26" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F26" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G26" s="1" t="s">
+      <c r="F26" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G26" s="1">
+        <v>646</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="I26" s="1">
+      <c r="J26" s="1">
         <v>7</v>
       </c>
-      <c r="J26" s="1">
+      <c r="K26" s="1">
         <v>8</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="L26" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L26" s="2" t="s">
+      <c r="M26" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="M26" s="2" t="s">
+      <c r="N26" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N26" s="2" t="s">
+      <c r="O26" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O26" s="2" t="s">
+      <c r="P26" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="P26" s="2" t="s">
+      <c r="Q26" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>13</v>
       </c>
@@ -2448,41 +2594,44 @@
       <c r="E27" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="F27" s="1">
-        <v>2018</v>
-      </c>
-      <c r="G27" s="1" t="s">
+      <c r="F27" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G27" s="1">
+        <v>610</v>
+      </c>
+      <c r="H27" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="I27" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="I27" s="1">
+      <c r="J27" s="1">
         <v>6</v>
       </c>
-      <c r="J27" s="1">
+      <c r="K27" s="1">
         <v>7</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="L27" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="L27" s="2" t="s">
+      <c r="M27" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="M27" s="2" t="s">
+      <c r="N27" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N27" s="2" t="s">
+      <c r="O27" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="O27" s="2" t="s">
+      <c r="P27" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="P27" s="2" t="s">
+      <c r="Q27" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>13</v>
       </c>
@@ -2498,41 +2647,44 @@
       <c r="E28" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="F28" s="1">
-        <v>2017</v>
-      </c>
-      <c r="G28" s="1" t="s">
+      <c r="F28" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G28" s="1">
+        <v>592</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="I28" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="I28" s="1">
+      <c r="J28" s="1">
         <v>6</v>
       </c>
-      <c r="J28" s="1">
+      <c r="K28" s="1">
         <v>8</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="L28" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L28" s="2" t="s">
+      <c r="M28" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="M28" s="2" t="s">
+      <c r="N28" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N28" s="2" t="s">
+      <c r="O28" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="O28" s="2" t="s">
+      <c r="P28" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="P28" s="2" t="s">
+      <c r="Q28" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>13</v>
       </c>
@@ -2548,41 +2700,44 @@
       <c r="E29" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F29" s="1">
-        <v>2016</v>
-      </c>
-      <c r="G29" s="1" t="s">
+      <c r="F29" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="G29" s="1">
+        <v>564</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="I29" s="1">
+      <c r="J29" s="1">
         <v>5</v>
       </c>
-      <c r="J29" s="1">
+      <c r="K29" s="1">
         <v>8</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="L29" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L29" s="2" t="s">
+      <c r="M29" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="M29" s="2" t="s">
+      <c r="N29" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="N29" s="2" t="s">
+      <c r="O29" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="O29" s="2" t="s">
+      <c r="P29" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="P29" s="2" t="s">
+      <c r="Q29" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>13</v>
       </c>
@@ -2596,43 +2751,46 @@
         <v>169</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="F30" s="1">
-        <v>2015</v>
-      </c>
-      <c r="G30" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="G30" s="1">
+        <v>542</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="I30" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="I30" s="1">
+      <c r="J30" s="1">
         <v>7</v>
       </c>
-      <c r="J30" s="1">
+      <c r="K30" s="1">
         <v>8</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="L30" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L30" s="2" t="s">
+      <c r="M30" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="M30" s="2" t="s">
+      <c r="N30" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N30" s="2" t="s">
+      <c r="O30" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="O30" s="2" t="s">
+      <c r="P30" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="P30" s="2" t="s">
+      <c r="Q30" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>13</v>
       </c>
@@ -2646,43 +2804,46 @@
         <v>169</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F31" s="1">
-        <v>2014</v>
-      </c>
-      <c r="G31" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G31" s="1">
+        <v>516</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="I31" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="I31" s="1">
+      <c r="J31" s="1">
         <v>5</v>
       </c>
-      <c r="J31" s="1">
+      <c r="K31" s="1">
         <v>7</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="L31" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="L31" s="2" t="s">
+      <c r="M31" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="N31" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="N31" s="2" t="s">
+      <c r="O31" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="O31" s="2" t="s">
+      <c r="P31" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="P31" s="2" t="s">
+      <c r="Q31" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>13</v>
       </c>
@@ -2696,43 +2857,46 @@
         <v>169</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="F32" s="1">
-        <v>2013</v>
-      </c>
-      <c r="G32" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="G32" s="1">
+        <v>500</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="I32" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="I32" s="1">
-        <v>4</v>
       </c>
       <c r="J32" s="1">
         <v>4</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="K32" s="1">
+        <v>4</v>
+      </c>
+      <c r="L32" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L32" s="2" t="s">
+      <c r="M32" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="M32" s="2" t="s">
+      <c r="N32" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N32" s="2" t="s">
+      <c r="O32" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="O32" s="2" t="s">
+      <c r="P32" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="P32" s="2" t="s">
+      <c r="Q32" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>13</v>
       </c>
@@ -2748,41 +2912,44 @@
       <c r="E33" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F33" s="1">
-        <v>2012</v>
-      </c>
-      <c r="G33" s="1" t="s">
+      <c r="F33" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G33" s="1">
+        <v>468</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="I33" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I33" s="1">
+      <c r="J33" s="1">
         <v>4</v>
       </c>
-      <c r="J33" s="1">
+      <c r="K33" s="1">
         <v>6</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="L33" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="L33" s="2" t="s">
+      <c r="M33" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="M33" s="2" t="s">
+      <c r="N33" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="N33" s="2" t="s">
+      <c r="O33" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="O33" s="2" t="s">
+      <c r="P33" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="P33" s="2" t="s">
+      <c r="Q33" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>13</v>
       </c>
@@ -2796,43 +2963,46 @@
         <v>169</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="F34" s="1">
-        <v>2011</v>
-      </c>
-      <c r="G34" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G34" s="1">
+        <v>426</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="I34" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="I34" s="1">
-        <v>10</v>
       </c>
       <c r="J34" s="1">
         <v>10</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="K34" s="1">
+        <v>10</v>
+      </c>
+      <c r="L34" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="L34" s="2" t="s">
+      <c r="M34" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="M34" s="2" t="s">
+      <c r="N34" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N34" s="2" t="s">
+      <c r="O34" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="O34" s="2" t="s">
+      <c r="P34" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="P34" s="2" t="s">
+      <c r="Q34" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>13</v>
       </c>
@@ -2846,40 +3016,43 @@
         <v>169</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="F35" s="1">
-        <v>2010</v>
-      </c>
-      <c r="G35" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="G35" s="1">
+        <v>412</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="I35" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I35" s="1">
+      <c r="J35" s="1">
         <v>4</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="L35" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L35" s="2" t="s">
+      <c r="M35" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="M35" s="2" t="s">
+      <c r="N35" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="N35" s="2" t="s">
+      <c r="O35" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="O35" s="2" t="s">
+      <c r="P35" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="P35" s="2" t="s">
+      <c r="Q35" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>13</v>
       </c>
@@ -2895,41 +3068,44 @@
       <c r="E36" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F36" s="1">
-        <v>2009</v>
-      </c>
-      <c r="G36" s="1" t="s">
+      <c r="F36" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="G36" s="1">
+        <v>319</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="I36" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="I36" s="1">
-        <v>21</v>
       </c>
       <c r="J36" s="1">
         <v>21</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="K36" s="1">
+        <v>21</v>
+      </c>
+      <c r="L36" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="L36" s="2" t="s">
+      <c r="M36" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="M36" s="2" t="s">
+      <c r="N36" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="N36" s="2" t="s">
+      <c r="O36" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="O36" s="2" t="s">
+      <c r="P36" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="P36" s="2" t="s">
+      <c r="Q36" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>13</v>
       </c>
@@ -2945,41 +3121,44 @@
       <c r="E37" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F37" s="1">
-        <v>2008</v>
-      </c>
-      <c r="G37" s="1" t="s">
+      <c r="F37" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="G37" s="1">
+        <v>254</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="I37" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I37" s="1">
+      <c r="J37" s="1">
         <v>19</v>
       </c>
-      <c r="J37" s="1">
+      <c r="K37" s="1">
         <v>21</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="L37" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="L37" s="2" t="s">
+      <c r="M37" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="M37" s="2" t="s">
+      <c r="N37" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="N37" s="2" t="s">
+      <c r="O37" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="O37" s="2" t="s">
+      <c r="P37" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="P37" s="2" t="s">
+      <c r="Q37" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>13</v>
       </c>
@@ -2995,41 +3174,44 @@
       <c r="E38" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F38" s="1">
-        <v>2007</v>
-      </c>
-      <c r="G38" s="1" t="s">
+      <c r="F38" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G38" s="1">
+        <v>321</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="I38" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I38" s="1">
+      <c r="J38" s="1">
         <v>17</v>
       </c>
-      <c r="J38" s="1">
+      <c r="K38" s="1">
         <v>23</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="L38" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="L38" s="2" t="s">
+      <c r="M38" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="M38" s="2" t="s">
+      <c r="N38" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="N38" s="2" t="s">
+      <c r="O38" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="O38" s="2" t="s">
+      <c r="P38" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="P38" s="2" t="s">
+      <c r="Q38" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>13</v>
       </c>
@@ -3045,41 +3227,44 @@
       <c r="E39" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="F39" s="1">
-        <v>2006</v>
-      </c>
-      <c r="G39" s="1" t="s">
+      <c r="F39" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G39" s="1">
+        <v>232</v>
+      </c>
+      <c r="H39" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="I39" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="I39" s="1">
+      <c r="J39" s="1">
         <v>21</v>
       </c>
-      <c r="J39" s="1">
+      <c r="K39" s="1">
         <v>22</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="L39" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="L39" s="2" t="s">
+      <c r="M39" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="M39" s="2" t="s">
+      <c r="N39" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="N39" s="2" t="s">
+      <c r="O39" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="O39" s="2" t="s">
+      <c r="P39" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="P39" s="2" t="s">
+      <c r="Q39" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>13</v>
       </c>
@@ -3095,38 +3280,41 @@
       <c r="E40" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F40" s="1">
-        <v>2005</v>
-      </c>
-      <c r="G40" s="1" t="s">
+      <c r="F40" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G40" s="1">
+        <v>230</v>
+      </c>
+      <c r="H40" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="I40" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I40" s="1">
+      <c r="J40" s="1">
         <v>19</v>
       </c>
-      <c r="J40" s="1">
+      <c r="K40" s="1">
         <v>24</v>
       </c>
-      <c r="K40" s="1" t="s">
+      <c r="L40" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="L40" s="2" t="s">
+      <c r="M40" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="M40" s="2" t="s">
+      <c r="N40" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="N40" s="2" t="s">
+      <c r="O40" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="O40" s="2" t="s">
+      <c r="P40" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>14</v>
       </c>
@@ -3140,40 +3328,43 @@
         <v>171</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F41" s="1">
-        <v>2022</v>
-      </c>
-      <c r="G41" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G41" s="1">
+        <v>717</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="I41" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I41" s="1">
+      <c r="J41" s="1">
         <v>32</v>
       </c>
-      <c r="J41" s="1">
+      <c r="K41" s="1">
         <v>35</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="L41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L41" s="2" t="s">
+      <c r="M41" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="M41" s="2" t="s">
+      <c r="N41" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="N41" s="2" t="s">
+      <c r="O41" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="O41" s="2" t="s">
+      <c r="P41" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>14</v>
       </c>
@@ -3187,40 +3378,43 @@
         <v>171</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F42" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G42" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G42" s="1">
+        <v>647</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="I42" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I42" s="1">
+      <c r="J42" s="1">
         <v>35</v>
       </c>
-      <c r="J42" s="1">
+      <c r="K42" s="1">
         <v>40</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="L42" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L42" s="2" t="s">
+      <c r="M42" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="M42" s="2" t="s">
+      <c r="N42" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="N42" s="2" t="s">
+      <c r="O42" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="O42" s="2" t="s">
+      <c r="P42" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>14</v>
       </c>
@@ -3234,40 +3428,43 @@
         <v>171</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="F43" s="1">
-        <v>2018</v>
-      </c>
-      <c r="G43" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G43" s="1">
+        <v>624</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="I43" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="I43" s="1">
-        <v>35</v>
       </c>
       <c r="J43" s="1">
         <v>35</v>
       </c>
-      <c r="K43" s="1" t="s">
+      <c r="K43" s="1">
+        <v>35</v>
+      </c>
+      <c r="L43" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L43" s="2" t="s">
+      <c r="M43" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="M43" s="2" t="s">
+      <c r="N43" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="N43" s="2" t="s">
+      <c r="O43" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="O43" s="2" t="s">
+      <c r="P43" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>14</v>
       </c>
@@ -3281,40 +3478,43 @@
         <v>171</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="F44" s="1">
-        <v>2017</v>
-      </c>
-      <c r="G44" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G44" s="1">
+        <v>593</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="I44" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="I44" s="1">
+      <c r="J44" s="1">
         <v>29</v>
       </c>
-      <c r="J44" s="1">
+      <c r="K44" s="1">
         <v>37</v>
       </c>
-      <c r="K44" s="1" t="s">
+      <c r="L44" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="L44" s="2" t="s">
+      <c r="M44" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M44" s="2" t="s">
+      <c r="N44" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="N44" s="2" t="s">
+      <c r="O44" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="O44" s="2" t="s">
+      <c r="P44" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>14</v>
       </c>
@@ -3328,40 +3528,43 @@
         <v>171</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="F45" s="1">
-        <v>2016</v>
-      </c>
-      <c r="G45" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G45" s="1">
+        <v>565</v>
+      </c>
+      <c r="H45" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="I45" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="I45" s="1">
+      <c r="J45" s="1">
         <v>30</v>
       </c>
-      <c r="J45" s="1">
+      <c r="K45" s="1">
         <v>37</v>
       </c>
-      <c r="K45" s="1" t="s">
+      <c r="L45" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L45" s="2" t="s">
+      <c r="M45" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M45" s="2" t="s">
+      <c r="N45" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N45" s="2" t="s">
+      <c r="O45" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="O45" s="2" t="s">
+      <c r="P45" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>14</v>
       </c>
@@ -3375,43 +3578,46 @@
         <v>172</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F46" s="1">
-        <v>2012</v>
-      </c>
-      <c r="G46" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G46" s="1">
+        <v>466</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="I46" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="I46" s="1">
-        <v>24</v>
       </c>
       <c r="J46" s="1">
         <v>24</v>
       </c>
-      <c r="K46" s="1" t="s">
+      <c r="K46" s="1">
+        <v>24</v>
+      </c>
+      <c r="L46" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L46" s="2" t="s">
+      <c r="M46" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M46" s="2" t="s">
+      <c r="N46" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N46" s="2" t="s">
+      <c r="O46" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="O46" s="2" t="s">
+      <c r="P46" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="P46" s="2" t="s">
+      <c r="Q46" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>14</v>
       </c>
@@ -3425,40 +3631,43 @@
         <v>172</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="F47" s="1">
-        <v>2007</v>
-      </c>
-      <c r="G47" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G47" s="1">
+        <v>322</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="I47" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="I47" s="1">
-        <v>24</v>
       </c>
       <c r="J47" s="1">
         <v>24</v>
       </c>
-      <c r="K47" s="1" t="s">
+      <c r="K47" s="1">
+        <v>24</v>
+      </c>
+      <c r="L47" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="L47" s="2" t="s">
+      <c r="M47" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M47" s="2" t="s">
+      <c r="N47" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="N47" s="2" t="s">
+      <c r="O47" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="O47" s="2" t="s">
+      <c r="P47" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>14</v>
       </c>
@@ -3472,40 +3681,43 @@
         <v>172</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F48" s="1">
-        <v>2005</v>
-      </c>
-      <c r="G48" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G48" s="1">
+        <v>301</v>
+      </c>
+      <c r="H48" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="I48" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="I48" s="1">
+      <c r="J48" s="1">
         <v>22</v>
       </c>
-      <c r="J48" s="1">
+      <c r="K48" s="1">
         <v>23</v>
       </c>
-      <c r="K48" s="1" t="s">
+      <c r="L48" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="L48" s="2" t="s">
+      <c r="M48" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M48" s="2" t="s">
+      <c r="N48" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="N48" s="2" t="s">
+      <c r="O48" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="O48" s="2" t="s">
+      <c r="P48" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>15</v>
       </c>
@@ -3519,34 +3731,37 @@
         <v>173</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="F49" s="1">
-        <v>2026</v>
-      </c>
-      <c r="G49" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G49" s="1">
+        <v>824</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="I49" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I49" s="1">
+      <c r="J49" s="1">
         <v>27</v>
       </c>
-      <c r="J49" s="1">
+      <c r="K49" s="1">
         <v>33</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="L49" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="L49" s="2" t="s">
+      <c r="M49" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="M49" s="2" t="s">
+      <c r="N49" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>15</v>
       </c>
@@ -3560,34 +3775,37 @@
         <v>173</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F50" s="1">
-        <v>2022</v>
-      </c>
-      <c r="G50" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G50" s="1">
+        <v>727</v>
+      </c>
+      <c r="H50" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="I50" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I50" s="1">
+      <c r="J50" s="1">
         <v>24</v>
       </c>
-      <c r="J50" s="1">
+      <c r="K50" s="1">
         <v>26</v>
       </c>
-      <c r="K50" s="1" t="s">
+      <c r="L50" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="L50" s="2" t="s">
+      <c r="M50" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M50" s="2" t="s">
+      <c r="N50" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>15</v>
       </c>
@@ -3601,34 +3819,37 @@
         <v>174</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="F51" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G51" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G51" s="1">
+        <v>641</v>
+      </c>
+      <c r="H51" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="I51" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="I51" s="1">
+      <c r="J51" s="1">
         <v>41</v>
       </c>
-      <c r="J51" s="1">
+      <c r="K51" s="1">
         <v>48</v>
       </c>
-      <c r="K51" s="1" t="s">
+      <c r="L51" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L51" s="2" t="s">
+      <c r="M51" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="M51" s="2" t="s">
+      <c r="N51" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>15</v>
       </c>
@@ -3644,32 +3865,35 @@
       <c r="E52" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="F52" s="1">
-        <v>2018</v>
-      </c>
-      <c r="G52" s="1" t="s">
+      <c r="F52" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G52" s="1">
+        <v>606</v>
+      </c>
+      <c r="H52" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H52" s="1" t="s">
+      <c r="I52" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="I52" s="1">
-        <v>40</v>
       </c>
       <c r="J52" s="1">
         <v>40</v>
       </c>
-      <c r="K52" s="1" t="s">
+      <c r="K52" s="1">
+        <v>40</v>
+      </c>
+      <c r="L52" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L52" s="2" t="s">
+      <c r="M52" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="M52" s="2" t="s">
+      <c r="N52" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>15</v>
       </c>
@@ -3683,34 +3907,37 @@
         <v>174</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F53" s="1">
-        <v>2017</v>
-      </c>
-      <c r="G53" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G53" s="1">
+        <v>583</v>
+      </c>
+      <c r="H53" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="I53" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I53" s="1">
+      <c r="J53" s="1">
         <v>37</v>
       </c>
-      <c r="J53" s="1">
+      <c r="K53" s="1">
         <v>39</v>
       </c>
-      <c r="K53" s="1" t="s">
+      <c r="L53" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L53" s="2" t="s">
+      <c r="M53" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M53" s="2" t="s">
+      <c r="N53" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>10</v>
       </c>
@@ -3726,41 +3953,44 @@
       <c r="E54" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="F54" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G54" s="1" t="s">
+      <c r="F54" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G54" s="1">
+        <v>656</v>
+      </c>
+      <c r="H54" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H54" s="1" t="s">
+      <c r="I54" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="I54" s="1">
-        <v>24</v>
       </c>
       <c r="J54" s="1">
         <v>24</v>
       </c>
-      <c r="K54" s="1" t="s">
+      <c r="K54" s="1">
+        <v>24</v>
+      </c>
+      <c r="L54" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L54" s="2" t="s">
+      <c r="M54" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="M54" s="2" t="s">
+      <c r="N54" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="N54" s="2" t="s">
+      <c r="O54" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="O54" s="2" t="s">
+      <c r="P54" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="P54" s="2" t="s">
+      <c r="Q54" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>13</v>
       </c>
@@ -3776,41 +4006,44 @@
       <c r="E55" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="F55" s="1">
-        <v>2024</v>
-      </c>
-      <c r="G55" s="1" t="s">
+      <c r="F55" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G55" s="1">
+        <v>782</v>
+      </c>
+      <c r="H55" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H55" s="1" t="s">
+      <c r="I55" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="I55" s="1">
-        <v>21</v>
       </c>
       <c r="J55" s="1">
         <v>21</v>
       </c>
-      <c r="K55" s="1" t="s">
+      <c r="K55" s="1">
+        <v>21</v>
+      </c>
+      <c r="L55" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L55" s="2" t="s">
+      <c r="M55" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="M55" s="2" t="s">
+      <c r="N55" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N55" s="2" t="s">
+      <c r="O55" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="O55" s="2" t="s">
+      <c r="P55" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="P55" s="2" t="s">
+      <c r="Q55" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>13</v>
       </c>
@@ -3826,41 +4059,44 @@
       <c r="E56" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="F56" s="1">
-        <v>2023</v>
-      </c>
-      <c r="G56" s="1" t="s">
+      <c r="F56" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G56" s="1">
+        <v>756</v>
+      </c>
+      <c r="H56" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H56" s="1" t="s">
+      <c r="I56" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="I56" s="1">
+      <c r="J56" s="1">
         <v>24</v>
       </c>
-      <c r="J56" s="1">
+      <c r="K56" s="1">
         <v>25</v>
       </c>
-      <c r="K56" s="1" t="s">
+      <c r="L56" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="L56" s="2" t="s">
+      <c r="M56" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="M56" s="2" t="s">
+      <c r="N56" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N56" s="2" t="s">
+      <c r="O56" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="O56" s="2" t="s">
+      <c r="P56" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="P56" s="2" t="s">
+      <c r="Q56" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>14</v>
       </c>
@@ -3874,40 +4110,43 @@
         <v>177</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F57" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G57" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G57" s="1">
+        <v>675</v>
+      </c>
+      <c r="H57" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H57" s="1" t="s">
+      <c r="I57" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="I57" s="1">
-        <v>14</v>
       </c>
       <c r="J57" s="1">
         <v>14</v>
       </c>
-      <c r="K57" s="1" t="s">
+      <c r="K57" s="1">
+        <v>14</v>
+      </c>
+      <c r="L57" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L57" s="2" t="s">
+      <c r="M57" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="M57" s="2" t="s">
+      <c r="N57" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="N57" s="2" t="s">
+      <c r="O57" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="O57" s="2" t="s">
+      <c r="P57" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>10</v>
       </c>
@@ -3923,41 +4162,44 @@
       <c r="E58" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F58" s="1">
-        <v>2024</v>
-      </c>
-      <c r="G58" s="1" t="s">
+      <c r="F58" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G58" s="1">
+        <v>766</v>
+      </c>
+      <c r="H58" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H58" s="1" t="s">
+      <c r="I58" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I58" s="1">
+      <c r="J58" s="1">
         <v>22</v>
       </c>
-      <c r="J58" s="1">
+      <c r="K58" s="1">
         <v>25</v>
       </c>
-      <c r="K58" s="1" t="s">
+      <c r="L58" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="L58" s="2" t="s">
+      <c r="M58" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="M58" s="2" t="s">
+      <c r="N58" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="N58" s="2" t="s">
+      <c r="O58" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="O58" s="2" t="s">
+      <c r="P58" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="P58" s="2" t="s">
+      <c r="Q58" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>10</v>
       </c>
@@ -3973,41 +4215,41 @@
       <c r="E59" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="F59" s="1">
-        <v>2018</v>
-      </c>
-      <c r="G59" s="1" t="s">
+      <c r="F59" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G59" s="1">
+        <v>607</v>
+      </c>
+      <c r="H59" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H59" s="1" t="s">
+      <c r="I59" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="I59" s="1">
-        <v>28</v>
       </c>
       <c r="J59" s="1">
         <v>28</v>
       </c>
-      <c r="K59" s="1" t="s">
+      <c r="K59" s="1">
+        <v>28</v>
+      </c>
+      <c r="L59" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L59" s="2" t="s">
+      <c r="M59" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M59" s="2" t="s">
+      <c r="N59" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="N59" s="2" t="s">
+      <c r="O59" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="O59" s="2" t="s">
+      <c r="P59" s="2" t="s">
         <v>70</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A41:K48">
-    <sortCondition descending="1" ref="F41:F48"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/wc-data.xlsx
+++ b/wc-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c9d1b39c11dd659/Dokumenti/Apps/phc-stat/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="652" documentId="8_{31E65144-C7D6-482C-BFB9-14E83E95C2F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{304FED25-3186-4C9F-95F9-AA938F387331}"/>
+  <xr:revisionPtr revIDLastSave="653" documentId="8_{31E65144-C7D6-482C-BFB9-14E83E95C2F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5EFEFF0-64D5-4B63-80A3-217DD52BDD4B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{BABAC88A-431C-4718-AB57-202BD2B77C54}"/>
   </bookViews>
@@ -3033,6 +3033,9 @@
       <c r="J35" s="1">
         <v>4</v>
       </c>
+      <c r="K35" s="1">
+        <v>5</v>
+      </c>
       <c r="L35" s="1" t="s">
         <v>50</v>
       </c>
